--- a/output/audit_reports/B2G_Original_Audit_Report.xlsx
+++ b/output/audit_reports/B2G_Original_Audit_Report.xlsx
@@ -588,16 +588,16 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="39" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
     <col width="44" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -668,12 +668,14 @@
           <t>HR-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>ทุกหน้าเนื้อหา</t>
+          <t>ข้อความเนื้อหา (body)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -683,32 +685,32 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>แถบหัวข้อสี (~40 แถบ) + ข้อความเนื้อหา (body)</t>
+          <t>ข้อความ body ขนาด 10–12pt ทั้งเล่ม</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>ขอบเขตที่ยังไม่ได้ตรวจระดับซูมรายกลิฟครบทุกจุด</t>
+          <t>เนื้อหาย่อย (หัวข้อ/แถบสี ตรวจซูมครบแล้วในรอบ 2)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>ตรวจระดับเต็มหน้า 150 DPI ครบทุกหน้า ไม่พบความผิดปกติ</t>
+          <t>รอบ 2 ซูมหัวข้อ/แถบสีครบ 365 บรรทัด — พบผิด 1 (TH-001) เท่านั้น; body ตรวจเต็มหน้าแล้วไม่พบผิดปกติ</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>ต้องยืนยันด้วยรอบ 2 (ซูมหัวข้อทุกแถบ) หรือ OCR/พิสูจน์อักษรโดยมนุษย์</t>
+          <t>แนะนำพิสูจน์อักษร body โดยมนุษย์เพื่อรับรอง 0 ขั้นสุดท้าย (ความเชื่อมั่นสูง: body ใช้ฟอนต์ NotoSansThai/CanvaSans ที่ render สม่ำเสมอทั้งเล่ม)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>ความเสี่ยงตกหล่น (TH-001 หลุดจากการตรวจเต็มหน้า จึงยังรับประกัน 0 ไม่ได้)</t>
+          <t>ความเสี่ยงตกหล่นที่เหลือ (เฉพาะ body)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>ต้องตรวจทาน</t>
+          <t>ต้องตรวจทาน (ต่ำ)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -718,7 +720,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>ต้องตรวจทานโดยมนุษย์ / รอบ 2</t>
+          <t>ต้องตรวจทานโดยมนุษย์ (body เท่านั้น)</t>
         </is>
       </c>
     </row>
@@ -729,7 +731,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>15</v>
@@ -739,7 +741,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>กล่องหัวข้อ SME (กลางค่อนล่าง)</t>
+          <t>กล่องหัวข้อ SME</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -749,32 +751,32 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>ถ้อยคำหัวข้อ “...ที่เชื่อม/แข่งขันได้” (อ่านไม่ชัด)</t>
+          <t>การส่งเสริมวิสาหกิจขนาดกลางและขนาดย่อมที่เข้มแข็ง แข่งขันได้ — ถูกต้อง</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>ตรวจถ้อยคำให้ตรงต้นฉบับ (น่าจะเป็น “ที่แข่งขันได้”)</t>
+          <t>(ถูกต้องแล้ว — การอ่าน “ที่เชื่อม” ในรอบ 1 เป็นการอ่านผิดที่ความละเอียดต่ำ)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>ถ้อยคำไม่ชัด (ตรวจความหมาย)</t>
+          <t>ไม่ใช่ข้อผิดพลาด (false positive รอบ 1)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>ต่ำ</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>ตรวจสายตา (ยังไม่ซูมยืนยัน)</t>
+          <t>ซูม 320% ยืนยัน</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>ต้องตรวจทานโดยมนุษย์</t>
+          <t>ตรวจแล้ว ถูกต้อง — ปิดรายการ</t>
         </is>
       </c>
     </row>

--- a/output/audit_reports/B2G_Original_Audit_Report.xlsx
+++ b/output/audit_reports/B2G_Original_Audit_Report.xlsx
@@ -590,14 +590,14 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="39" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="44" customWidth="1" min="11" max="11"/>
-    <col width="36" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -670,7 +670,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -685,42 +685,42 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>ข้อความ body ขนาด 10–12pt ทั้งเล่ม</t>
+          <t>ข้อความ body 10–12pt ทั้งเล่ม</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>เนื้อหาย่อย (หัวข้อ/แถบสี ตรวจซูมครบแล้วในรอบ 2)</t>
+          <t>เนื้อหาย่อย body (หัวข้อ/แถบสีตรวจซูมครบในรอบ 2)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>รอบ 2 ซูมหัวข้อ/แถบสีครบ 365 บรรทัด — พบผิด 1 (TH-001) เท่านั้น; body ตรวจเต็มหน้าแล้วไม่พบผิดปกติ</t>
+          <t>รอบ 3 OCR ไทย (tesseract tha) + ตรวจพจนานุกรม pythainlp: 464 flag → 277 เป็นคำจริง (OCR เพี้ยน) → เหลือ 94 token → ตรวจทุก token เป็น OCR เพี้ยนของคำที่ถูกต้องทั้งหมด</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>แนะนำพิสูจน์อักษร body โดยมนุษย์เพื่อรับรอง 0 ขั้นสุดท้าย (ความเชื่อมั่นสูง: body ใช้ฟอนต์ NotoSansThai/CanvaSans ที่ render สม่ำเสมอทั้งเล่ม)</t>
+          <t>(body ถูกต้อง — ไม่พบข้อผิดพลาดต้นฉบับแม้แต่จุดเดียว)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>ความเสี่ยงตกหล่นที่เหลือ (เฉพาะ body)</t>
+          <t>ไม่พบข้อผิดพลาด (OCR noise ล้วน)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>ต้องตรวจทาน (ต่ำ)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>หลักการ QA: ห้ามอ้าง 0 โดยไม่มีหลักฐานรายจุด</t>
+          <t>OCR+พจนานุกรม+ซูมยืนยัน (ดู data/verification_results/needs_review.md)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>ต้องตรวจทานโดยมนุษย์ (body เท่านั้น)</t>
+          <t>ตรวจแล้ว body 0 errors — ปิดรายการ</t>
         </is>
       </c>
     </row>

--- a/output/audit_reports/B2G_Original_Audit_Report.xlsx
+++ b/output/audit_reports/B2G_Original_Audit_Report.xlsx
@@ -437,21 +437,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="39" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
     <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -519,56 +519,116 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>DISPLAY-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>ทั้งเล่ม (systemic)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>ทั้งเล่ม</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>ข้อความไทยจำนวนมากทั่วเล่ม</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>การวางตำแหน่งสระบน/วรรณยุกต์ (combining marks)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>สระ/วรรณยุกต์ลอยไปทับตัวถัดไป เมื่อเปิดด้วย viewer มือถือ/เว็บ (เช่นที่ bb.go.th, in-app browser) — ผู้ใช้ยืนยันด้วยภาพหน้าจอจริง (หน้า 7 'ปัญหา'→'ปั ญ')</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>แสดงผลถูกต้องทุก viewer</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>สระ/วรรณยุกต์ลอย (renderer-dependent; Canva Thai export ไม่ robust)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>สูงมาก (กระทบทั้งเล่ม + ผู้อ่านหลักใช้มือถือ)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>ผู้ใช้รายงาน + เทียบ render: viewer มือถือลอย แต่ MuPDF/Adobe ถูก → ยืนยัน renderer-dependent</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>แก้แล้วใน B2G_Repaired_Final.pdf (rasterize เป็นภาพ → ไม่มี text layer ให้ลอย)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>TH-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C3" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D3" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>หัวเรื่องใหญ่ บรรทัดที่ 2 (กลาง-บนหน้า)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>หัวเรื่องหมวด (Section title) — ด้านการบริหารภาครัฐ ...</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>การปฏฐูปกฎหมาย (สระ ิ หาย + ร เพี้ยนเป็น ฐ)</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>การปฏิรูปกฎหมาย</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>สระ/อักขระหาย + อักขระเพี้ยน (อ่านผิดจากต้นฉบับ)</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>สูง (หัวเรื่องหมวดหลัก)</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>ตรวจสายตา + ซูม 600% + ตรวจฟอนต์รายสแปน (NotoSansThai-Bold เดียวกับหน้า 68 แต่กลิฟต่างกัน) เทียบกับสารบัญ/หน้า 68</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>ยืนยันแล้ว — รอแก้ใน Canva</t>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>แก้แล้วใน B2G_Repaired_Final.pdf (overlay 'การปฏิรูปกฎหมาย' เบคเป็นภาพ); ฉบับ Canva ต้นฉบับยังควรแก้ถ้าต้องการ text แบบ select ได้</t>
         </is>
       </c>
     </row>

--- a/output/audit_reports/B2G_Original_Audit_Report.xlsx
+++ b/output/audit_reports/B2G_Original_Audit_Report.xlsx
@@ -437,17 +437,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="39" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="45" customWidth="1" min="10" max="10"/>
     <col width="45" customWidth="1" min="11" max="11"/>
@@ -579,54 +579,114 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>DATA-001</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>ทั้งเล่ม (ตัวเลขล้านบาท)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>ทั้งเล่ม</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>ตัวเลขงบประมาณหน่วยล้านบาท 252 จุด</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>รูปแบบทศนิยมของตัวเลขล้านบาท</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>ตัวเลขล้านบาทแสดง 0-2 ทศนิยม (เช่น 69,078.7) — ไม่เป็นมาตรฐาน 4 ตำแหน่ง; รวม 251/252 จุดไม่ครบ 4 ทศนิยม</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>รูปแบบ #,##0.0000 (4 ทศนิยม + comma) เช่น 69,078.7000 (ใช้ค่าเดิม ไม่แก้ค่า)</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>รูปแบบตัวเลข (ทศนิยมไม่ครบ 4 ตำแหน่งตามมาตรฐานล้านบาท)</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>สูง (ผู้ใช้/สำนักงบประมาณยืนยันมาตรฐาน)</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>ดึงเลขจาก text layer + แยกหน่วยจาก OCR (ดู B2G_Numbers_Audit.xlsx); ผลรวมตรงทุกหน้าที่ตรวจ → ค่าถูก แต่รูปแบบผิด</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>มีตารางครบ 453 จุด + รูปแบบที่ถูก; รอจัดรูปแบบลง PDF (เริ่มแล้ว: ตัวอย่างหน้า 22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>TH-001</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C4" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D4" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>หัวเรื่องใหญ่ บรรทัดที่ 2 (กลาง-บนหน้า)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>หัวเรื่องหมวด (Section title) — ด้านการบริหารภาครัฐ ...</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>การปฏฐูปกฎหมาย (สระ ิ หาย + ร เพี้ยนเป็น ฐ)</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>การปฏิรูปกฎหมาย</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>สระ/อักขระหาย + อักขระเพี้ยน (อ่านผิดจากต้นฉบับ)</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>สูง (หัวเรื่องหมวดหลัก)</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>ตรวจสายตา + ซูม 600% + ตรวจฟอนต์รายสแปน (NotoSansThai-Bold เดียวกับหน้า 68 แต่กลิฟต่างกัน) เทียบกับสารบัญ/หน้า 68</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>แก้แล้วใน B2G_Repaired_Final.pdf (overlay 'การปฏิรูปกฎหมาย' เบคเป็นภาพ); ฉบับ Canva ต้นฉบับยังควรแก้ถ้าต้องการ text แบบ select ได้</t>
         </is>

--- a/output/audit_reports/B2G_Original_Audit_Report.xlsx
+++ b/output/audit_reports/B2G_Original_Audit_Report.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>ตัวเลขล้านบาทแสดง 0-2 ทศนิยม (เช่น 69,078.7) — ไม่เป็นมาตรฐาน 4 ตำแหน่ง; รวม 251/252 จุดไม่ครบ 4 ทศนิยม</t>
+          <t>ตัวเลขล้านบาทแสดง 0-2 ทศนิยม (เช่น 69,078.7) — ไม่เป็นมาตรฐาน 4 ตำแหน่ง</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -627,12 +627,12 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>ดึงเลขจาก text layer + แยกหน่วยจาก OCR (ดู B2G_Numbers_Audit.xlsx); ผลรวมตรงทุกหน้าที่ตรวจ → ค่าถูก แต่รูปแบบผิด</t>
+          <t>ดึงเลขจาก text layer + แยกหน่วยแบบ nearest-keyword จาก OCR (กัน ล้านคน/พันล้านบาท/บาทต่อคน/GDP); ดู B2G_Numbers_Audit.xlsx</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>มีตารางครบ 453 จุด + รูปแบบที่ถูก; รอจัดรูปแบบลง PDF (เริ่มแล้ว: ตัวอย่างหน้า 22)</t>
+          <t>453 จุดในตาราง: ล้านบาทชัดเจน 120 → จัด 4 ทศนิยมลง PDF แล้ว 119 จุด (fit-to-box ไม่ทับ layout); ต้องตรวจทาน 137 จุด (เลขจำนวนเต็ม/พันล้าน/กำกวม — ไม่เดา)</t>
         </is>
       </c>
     </row>

--- a/output/audit_reports/B2G_Original_Audit_Report.xlsx
+++ b/output/audit_reports/B2G_Original_Audit_Report.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>453 จุดในตาราง: ล้านบาทชัดเจน 120 → จัด 4 ทศนิยมลง PDF แล้ว 119 จุด (fit-to-box ไม่ทับ layout); ต้องตรวจทาน 137 จุด (เลขจำนวนเต็ม/พันล้าน/กำกวม — ไม่เดา)</t>
+          <t>453 จุด: ล้านบาท 149 จุด → จัด 4 ทศนิยมลง PDF แล้ว 148 จุด (fit-to-box ไม่ทับ layout, รวม badge/ตาราง/inline/เลขก้อนใหญ่); กัน ล้านคน/ไร่/ครั้ง/พันล้านบาท/บาทต่อคน ถูกต้อง; เหลือ ~114 จุดให้ตรวจทาน (กำกวม/OCR ไม่จับ เช่น 151,520)</t>
         </is>
       </c>
     </row>

--- a/output/audit_reports/B2G_Original_Audit_Report.xlsx
+++ b/output/audit_reports/B2G_Original_Audit_Report.xlsx
@@ -607,32 +607,32 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>ตัวเลขล้านบาทแสดง 0-2 ทศนิยม (เช่น 69,078.7) — ไม่เป็นมาตรฐาน 4 ตำแหน่ง</t>
+          <t>ตัวเลขล้านบาทบางส่วนจุดทศนิยมเลื่อน (เช่น หมุดหมาย 69,078.7 ที่ถูกคือ 69.0787 ล้านบาท)</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>รูปแบบ #,##0.0000 (4 ทศนิยม + comma) เช่น 69,078.7000 (ใช้ค่าเดิม ไม่แก้ค่า)</t>
+          <t>กฎผู้ตรวจ: ใช้ตัวเลขเดิม วางจุดให้เหลือ 4 หลักหลังจุด (ไม่เติม 0 ไม่แก้ค่า) เช่น 69,078.7 → 69.0787</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>รูปแบบตัวเลข (ทศนิยมไม่ครบ 4 ตำแหน่งตามมาตรฐานล้านบาท)</t>
+          <t>รูปแบบ/ตำแหน่งจุดทศนิยมของตัวเลขล้านบาท (ปนกัน 2 แบบในเล่ม)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>สูง (ผู้ใช้/สำนักงบประมาณยืนยันมาตรฐาน)</t>
+          <t>บันทึกไว้ (ผู้ตรวจตัดสินใจไม่แก้)</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>ดึงเลขจาก text layer + แยกหน่วยแบบ nearest-keyword จาก OCR (กัน ล้านคน/พันล้านบาท/บาทต่อคน/GDP); ดู B2G_Numbers_Audit.xlsx</t>
+          <t>ดึงเลขจาก text layer + แยกหน่วยจาก OCR; ดู B2G_Numbers_Audit.xlsx (อ้างอิงเฉย ๆ)</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>453 จุด: ล้านบาท 149 จุด → จัด 4 ทศนิยมลง PDF แล้ว 148 จุด (fit-to-box ไม่ทับ layout, รวม badge/ตาราง/inline/เลขก้อนใหญ่); กัน ล้านคน/ไร่/ครั้ง/พันล้านบาท/บาทต่อคน ถูกต้อง; เหลือ ~114 จุดให้ตรวจทาน (กำกวม/OCR ไม่จับ เช่น 151,520)</t>
+          <t>ผู้ตรวจตัดสินใจ: คงตัวเลขตามต้นฉบับ 100% ไม่แก้/ไม่เดา (เราไม่ทราบค่าจริง) — บันทึกไว้เป็นข้อสังเกตเท่านั้น ไม่นับเป็นรายการที่ต้องแก้</t>
         </is>
       </c>
     </row>
